--- a/data/actividades.xlsx
+++ b/data/actividades.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dma01\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:80001_{7922EACB-2471-4EF4-8CB2-D313A494D8A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:80001_{90E4DE08-47CD-49DB-B954-C605906CC16E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="150" windowWidth="18480" windowHeight="9735" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,13 @@
     <sheet name="DMA" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DMA!$A$1:$AH$115</definedName>
     <definedName name="SegmentaciónDeDatos_Codigo" localSheetId="1">#REF!</definedName>
     <definedName name="SegmentaciónDeDatos_Codigo">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="215" r:id="rId3"/>
+    <pivotCache cacheId="221" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
@@ -842,19 +843,7 @@
     <t>Elaboración de pronósticos meteorológicos, climáticos y ambientales atmosféricos</t>
   </si>
   <si>
-    <t>DMCA</t>
-  </si>
-  <si>
-    <t>SVA</t>
-  </si>
-  <si>
-    <t>SVC</t>
-  </si>
-  <si>
     <t>BOLETIN</t>
-  </si>
-  <si>
-    <t>SVM</t>
   </si>
   <si>
     <t>AOI00047400643</t>
@@ -891,6 +880,18 @@
   </si>
   <si>
     <t>Articulación interinstitucional y vigilancia ambiental atmosférica para la generación de pronósticos y vigilancia ante eventos extremos en el marco del FEN</t>
+  </si>
+  <si>
+    <t>DMA</t>
+  </si>
+  <si>
+    <t>SPC</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>SPM</t>
   </si>
 </sst>
 </file>
@@ -6411,7 +6412,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="Resumen" cacheId="215" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="5" compact="0" compactData="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="Resumen" cacheId="221" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="" updatedVersion="5" compact="0" compactData="0">
   <location ref="A3:C54" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="35">
     <pivotField name="Meta pptal" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0"/>
@@ -9744,7 +9745,7 @@
         <v>37</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I2" s="34">
         <v>0</v>
@@ -9842,7 +9843,7 @@
         <v>35</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I3" s="34">
         <v>1</v>
@@ -9940,7 +9941,7 @@
         <v>37</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I4" s="34">
         <v>0</v>
@@ -10038,7 +10039,7 @@
         <v>37</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I5" s="34">
         <v>0</v>
@@ -10136,7 +10137,7 @@
         <v>37</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I6" s="34">
         <v>0</v>
@@ -10234,7 +10235,7 @@
         <v>101</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I7" s="34">
         <v>0</v>
@@ -10332,7 +10333,7 @@
         <v>35</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I8" s="34">
         <v>0</v>
@@ -10430,7 +10431,7 @@
         <v>35</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I9" s="34">
         <v>0</v>
@@ -10528,7 +10529,7 @@
         <v>101</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I10" s="34">
         <v>0</v>
@@ -10626,7 +10627,7 @@
         <v>105</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I11" s="34">
         <v>15</v>
@@ -10724,7 +10725,7 @@
         <v>107</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I12" s="34">
         <v>0</v>
@@ -10822,7 +10823,7 @@
         <v>112</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I13" s="34">
         <v>0</v>
@@ -10920,7 +10921,7 @@
         <v>101</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I14" s="34">
         <v>0</v>
@@ -11018,7 +11019,7 @@
         <v>101</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I15" s="34">
         <v>0</v>
@@ -11116,7 +11117,7 @@
         <v>117</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I16" s="34">
         <v>31</v>
@@ -11214,7 +11215,7 @@
         <v>107</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I17" s="34">
         <v>0</v>
@@ -11312,7 +11313,7 @@
         <v>101</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I18" s="34">
         <v>0</v>
@@ -11410,7 +11411,7 @@
         <v>101</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I19" s="34">
         <v>0</v>
@@ -11508,7 +11509,7 @@
         <v>101</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I20" s="34">
         <v>0</v>
@@ -11606,7 +11607,7 @@
         <v>101</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I21" s="34">
         <v>1</v>
@@ -11704,7 +11705,7 @@
         <v>101</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I22" s="34">
         <v>0</v>
@@ -11802,7 +11803,7 @@
         <v>101</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I23" s="34">
         <v>1</v>
@@ -11900,7 +11901,7 @@
         <v>101</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I24" s="34">
         <v>1</v>
@@ -11998,7 +11999,7 @@
         <v>35</v>
       </c>
       <c r="H25" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I25" s="34">
         <v>0</v>
@@ -12096,7 +12097,7 @@
         <v>35</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I26" s="34">
         <v>1</v>
@@ -12194,7 +12195,7 @@
         <v>35</v>
       </c>
       <c r="H27" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I27" s="34">
         <v>0</v>
@@ -12292,7 +12293,7 @@
         <v>101</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I28" s="34">
         <v>1</v>
@@ -12390,7 +12391,7 @@
         <v>101</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I29" s="34">
         <v>0</v>
@@ -12488,7 +12489,7 @@
         <v>139</v>
       </c>
       <c r="H30" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I30" s="34">
         <v>0</v>
@@ -12586,7 +12587,7 @@
         <v>139</v>
       </c>
       <c r="H31" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I31" s="34">
         <v>0</v>
@@ -12684,7 +12685,7 @@
         <v>37</v>
       </c>
       <c r="H32" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I32" s="34">
         <v>0</v>
@@ -12781,7 +12782,7 @@
         <v>139</v>
       </c>
       <c r="H33" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I33" s="34">
         <v>0</v>
@@ -12879,7 +12880,7 @@
         <v>146</v>
       </c>
       <c r="H34" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I34" s="34">
         <v>0</v>
@@ -12977,7 +12978,7 @@
         <v>146</v>
       </c>
       <c r="H35" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I35" s="34">
         <v>0</v>
@@ -13075,7 +13076,7 @@
         <v>101</v>
       </c>
       <c r="H36" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I36" s="34">
         <v>0</v>
@@ -13173,7 +13174,7 @@
         <v>146</v>
       </c>
       <c r="H37" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I37" s="34">
         <v>0</v>
@@ -13270,7 +13271,7 @@
         <v>146</v>
       </c>
       <c r="H38" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I38" s="34">
         <v>0</v>
@@ -13367,7 +13368,7 @@
         <v>146</v>
       </c>
       <c r="H39" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I39" s="34">
         <v>0</v>
@@ -13465,7 +13466,7 @@
         <v>146</v>
       </c>
       <c r="H40" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I40" s="34">
         <v>0</v>
@@ -13563,7 +13564,7 @@
         <v>146</v>
       </c>
       <c r="H41" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I41" s="34">
         <v>0</v>
@@ -13661,7 +13662,7 @@
         <v>146</v>
       </c>
       <c r="H42" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I42" s="34">
         <v>0</v>
@@ -13759,7 +13760,7 @@
         <v>146</v>
       </c>
       <c r="H43" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I43" s="34">
         <v>0</v>
@@ -13857,7 +13858,7 @@
         <v>146</v>
       </c>
       <c r="H44" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I44" s="34">
         <v>0</v>
@@ -13954,7 +13955,7 @@
         <v>146</v>
       </c>
       <c r="H45" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I45" s="34">
         <v>0</v>
@@ -14052,7 +14053,7 @@
         <v>146</v>
       </c>
       <c r="H46" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I46" s="34">
         <v>0</v>
@@ -14149,7 +14150,7 @@
         <v>146</v>
       </c>
       <c r="H47" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I47" s="34">
         <v>0</v>
@@ -14247,7 +14248,7 @@
         <v>146</v>
       </c>
       <c r="H48" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I48" s="34">
         <v>0</v>
@@ -14345,7 +14346,7 @@
         <v>101</v>
       </c>
       <c r="H49" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I49" s="34">
         <v>0</v>
@@ -14443,7 +14444,7 @@
         <v>146</v>
       </c>
       <c r="H50" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I50" s="34">
         <v>0</v>
@@ -14541,7 +14542,7 @@
         <v>146</v>
       </c>
       <c r="H51" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I51" s="34">
         <v>0</v>
@@ -14638,7 +14639,7 @@
         <v>146</v>
       </c>
       <c r="H52" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I52" s="34">
         <v>0</v>
@@ -14736,7 +14737,7 @@
         <v>146</v>
       </c>
       <c r="H53" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I53" s="34">
         <v>0</v>
@@ -14834,7 +14835,7 @@
         <v>146</v>
       </c>
       <c r="H54" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I54" s="34">
         <v>0</v>
@@ -14932,7 +14933,7 @@
         <v>146</v>
       </c>
       <c r="H55" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I55" s="34">
         <v>0</v>
@@ -15030,7 +15031,7 @@
         <v>146</v>
       </c>
       <c r="H56" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I56" s="34">
         <v>0</v>
@@ -15128,7 +15129,7 @@
         <v>146</v>
       </c>
       <c r="H57" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I57" s="34">
         <v>0</v>
@@ -15226,7 +15227,7 @@
         <v>146</v>
       </c>
       <c r="H58" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I58" s="34">
         <v>0</v>
@@ -15324,7 +15325,7 @@
         <v>146</v>
       </c>
       <c r="H59" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I59" s="34">
         <v>0</v>
@@ -15422,7 +15423,7 @@
         <v>146</v>
       </c>
       <c r="H60" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I60" s="34">
         <v>0</v>
@@ -15520,7 +15521,7 @@
         <v>146</v>
       </c>
       <c r="H61" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I61" s="34">
         <v>0</v>
@@ -15618,7 +15619,7 @@
         <v>146</v>
       </c>
       <c r="H62" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I62" s="34">
         <v>0</v>
@@ -15716,7 +15717,7 @@
         <v>146</v>
       </c>
       <c r="H63" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I63" s="34">
         <v>0</v>
@@ -15814,7 +15815,7 @@
         <v>146</v>
       </c>
       <c r="H64" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I64" s="34">
         <v>0</v>
@@ -15912,7 +15913,7 @@
         <v>146</v>
       </c>
       <c r="H65" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I65" s="34">
         <v>0</v>
@@ -16010,7 +16011,7 @@
         <v>146</v>
       </c>
       <c r="H66" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I66" s="34">
         <v>0</v>
@@ -16108,7 +16109,7 @@
         <v>146</v>
       </c>
       <c r="H67" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I67" s="34">
         <v>0</v>
@@ -16206,7 +16207,7 @@
         <v>35</v>
       </c>
       <c r="H68" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I68" s="34">
         <v>0</v>
@@ -16304,7 +16305,7 @@
         <v>35</v>
       </c>
       <c r="H69" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I69" s="39">
         <v>0</v>
@@ -16402,7 +16403,7 @@
         <v>35</v>
       </c>
       <c r="H70" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I70" s="34">
         <v>2</v>
@@ -16500,7 +16501,7 @@
         <v>107</v>
       </c>
       <c r="H71" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I71" s="34">
         <v>0</v>
@@ -16598,7 +16599,7 @@
         <v>35</v>
       </c>
       <c r="H72" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I72" s="34">
         <v>0</v>
@@ -16696,7 +16697,7 @@
         <v>101</v>
       </c>
       <c r="H73" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I73" s="34">
         <v>0</v>
@@ -16794,7 +16795,7 @@
         <v>117</v>
       </c>
       <c r="H74" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I74" s="34">
         <v>3</v>
@@ -16892,7 +16893,7 @@
         <v>101</v>
       </c>
       <c r="H75" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I75" s="39">
         <v>0</v>
@@ -16990,7 +16991,7 @@
         <v>210</v>
       </c>
       <c r="H76" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I76" s="34">
         <v>1</v>
@@ -17088,7 +17089,7 @@
         <v>212</v>
       </c>
       <c r="H77" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I77" s="34">
         <v>12</v>
@@ -17183,10 +17184,10 @@
         <v>213</v>
       </c>
       <c r="G78" s="31" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H78" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I78" s="34">
         <v>15</v>
@@ -17284,7 +17285,7 @@
         <v>101</v>
       </c>
       <c r="H79" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I79" s="34">
         <v>1</v>
@@ -17379,10 +17380,10 @@
         <v>215</v>
       </c>
       <c r="G80" s="31" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H80" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I80" s="34">
         <v>2</v>
@@ -17480,7 +17481,7 @@
         <v>35</v>
       </c>
       <c r="H81" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I81" s="34">
         <v>0</v>
@@ -17578,7 +17579,7 @@
         <v>37</v>
       </c>
       <c r="H82" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I82" s="34">
         <v>1</v>
@@ -17676,7 +17677,7 @@
         <v>35</v>
       </c>
       <c r="H83" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I83" s="34">
         <v>0</v>
@@ -17774,7 +17775,7 @@
         <v>35</v>
       </c>
       <c r="H84" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I84" s="34">
         <v>0</v>
@@ -17872,7 +17873,7 @@
         <v>35</v>
       </c>
       <c r="H85" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I85" s="34">
         <v>0</v>
@@ -17970,7 +17971,7 @@
         <v>35</v>
       </c>
       <c r="H86" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I86" s="34">
         <v>0</v>
@@ -18068,7 +18069,7 @@
         <v>35</v>
       </c>
       <c r="H87" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I87" s="34">
         <v>1</v>
@@ -18166,7 +18167,7 @@
         <v>117</v>
       </c>
       <c r="H88" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I88" s="34">
         <v>31</v>
@@ -18264,7 +18265,7 @@
         <v>101</v>
       </c>
       <c r="H89" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I89" s="34">
         <v>0</v>
@@ -18362,7 +18363,7 @@
         <v>117</v>
       </c>
       <c r="H90" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I90" s="34">
         <v>22</v>
@@ -18460,7 +18461,7 @@
         <v>35</v>
       </c>
       <c r="H91" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I91" s="34">
         <v>0</v>
@@ -18558,7 +18559,7 @@
         <v>107</v>
       </c>
       <c r="H92" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I92" s="34">
         <v>0</v>
@@ -18656,7 +18657,7 @@
         <v>35</v>
       </c>
       <c r="H93" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I93" s="34">
         <v>0</v>
@@ -18754,7 +18755,7 @@
         <v>35</v>
       </c>
       <c r="H94" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I94" s="34">
         <v>31</v>
@@ -18849,10 +18850,10 @@
         <v>233</v>
       </c>
       <c r="G95" s="31" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H95" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I95" s="34">
         <v>0</v>
@@ -18947,10 +18948,10 @@
         <v>234</v>
       </c>
       <c r="G96" s="31" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H96" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I96" s="34">
         <v>5</v>
@@ -19048,7 +19049,7 @@
         <v>35</v>
       </c>
       <c r="H97" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I97" s="34">
         <v>0</v>
@@ -19146,7 +19147,7 @@
         <v>35</v>
       </c>
       <c r="H98" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I98" s="34">
         <v>0</v>
@@ -19244,7 +19245,7 @@
         <v>35</v>
       </c>
       <c r="H99" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I99" s="34">
         <v>0</v>
@@ -19342,7 +19343,7 @@
         <v>35</v>
       </c>
       <c r="H100" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I100" s="34">
         <v>0</v>
@@ -19440,7 +19441,7 @@
         <v>37</v>
       </c>
       <c r="H101" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I101" s="34">
         <v>0</v>
@@ -19538,7 +19539,7 @@
         <v>37</v>
       </c>
       <c r="H102" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I102" s="34">
         <v>0</v>
@@ -19636,7 +19637,7 @@
         <v>37</v>
       </c>
       <c r="H103" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I103" s="34">
         <v>0</v>
@@ -19731,10 +19732,10 @@
         <v>245</v>
       </c>
       <c r="G104" s="31" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="H104" s="33" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I104" s="34">
         <v>1</v>
@@ -19832,7 +19833,7 @@
         <v>37</v>
       </c>
       <c r="H105" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I105" s="39">
         <v>0</v>
@@ -19930,7 +19931,7 @@
         <v>35</v>
       </c>
       <c r="H106" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I106" s="39">
         <v>0</v>
@@ -20028,7 +20029,7 @@
         <v>35</v>
       </c>
       <c r="H107" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I107" s="39">
         <v>0</v>
@@ -20126,7 +20127,7 @@
         <v>37</v>
       </c>
       <c r="H108" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I108" s="39">
         <v>0</v>
@@ -20224,7 +20225,7 @@
         <v>101</v>
       </c>
       <c r="H109" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I109" s="34">
         <v>0</v>
@@ -20322,7 +20323,7 @@
         <v>117</v>
       </c>
       <c r="H110" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I110" s="34">
         <v>16</v>
@@ -20420,7 +20421,7 @@
         <v>37</v>
       </c>
       <c r="H111" s="33" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I111" s="48">
         <v>0</v>
@@ -20500,23 +20501,23 @@
         <v>134</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C112" s="19"/>
       <c r="D112" s="32" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E112" s="31" t="s">
         <v>37</v>
       </c>
       <c r="F112" s="51" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G112" s="52" t="s">
         <v>37</v>
       </c>
       <c r="H112" s="53" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I112" s="39">
         <v>0</v>
@@ -20582,23 +20583,23 @@
         <v>135</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C113" s="20"/>
       <c r="D113" s="32" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="E113" s="31" t="s">
         <v>37</v>
       </c>
       <c r="F113" s="51" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="G113" s="52" t="s">
         <v>37</v>
       </c>
       <c r="H113" s="53" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="I113" s="39">
         <v>0</v>
@@ -20675,25 +20676,25 @@
         <v>136</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C114" s="20" t="s">
         <v>263</v>
       </c>
       <c r="D114" s="32" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E114" s="31" t="s">
         <v>37</v>
       </c>
       <c r="F114" s="51" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G114" s="52" t="s">
         <v>37</v>
       </c>
       <c r="H114" s="53" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="I114" s="39">
         <v>0</v>
@@ -20770,23 +20771,23 @@
         <v>139</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C115" s="19"/>
       <c r="D115" s="32" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E115" s="31" t="s">
         <v>37</v>
       </c>
       <c r="F115" s="51" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G115" s="55" t="s">
         <v>37</v>
       </c>
       <c r="H115" s="56" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="I115" s="39">
         <v>0</v>
@@ -29207,6 +29208,7 @@
       <c r="AC962" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AH115" xr:uid="{BBA8BC29-2D6B-4BC3-ACE7-CE3D6550DA2B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="35" orientation="landscape" r:id="rId1"/>
 </worksheet>
